--- a/public/template-import/TEMPLATE_IMPORT_PROJECT_LEGACY_KOBRA.xlsx
+++ b/public/template-import/TEMPLATE_IMPORT_PROJECT_LEGACY_KOBRA.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowHeight="18160"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="21">
   <si>
     <t>IMPORT DATA PROJECT LEGACY</t>
   </si>
@@ -45,6 +45,9 @@
   </si>
   <si>
     <t>DIVISION_CODE_INITIATION</t>
+  </si>
+  <si>
+    <t>GROUP_CODE_INVOLVED</t>
   </si>
   <si>
     <t>PROJET_TYPE</t>
@@ -658,191 +661,189 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1380,32 +1381,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="35.21875" customWidth="1"/>
-    <col min="2" max="2" width="40.4453125" customWidth="1"/>
-    <col min="3" max="3" width="25.6640625" customWidth="1"/>
-    <col min="4" max="4" width="24.3359375" customWidth="1"/>
-    <col min="5" max="5" width="28.890625" customWidth="1"/>
-    <col min="6" max="8" width="23.21875" customWidth="1"/>
-    <col min="9" max="9" width="25.78125" customWidth="1"/>
+    <col min="1" max="1" width="35.21875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="40.4453125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="25.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="24.3359375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="28.890625" style="2" customWidth="1"/>
+    <col min="6" max="8" width="23.21875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="25.78125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="25.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.4" spans="1:9">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="20.4" customHeight="1" spans="1:1">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:10">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -1424,8 +1418,8 @@
       <c r="F2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="9" t="s">
-        <v>2</v>
+      <c r="G2" s="4" t="s">
+        <v>1</v>
       </c>
       <c r="H2" s="9" t="s">
         <v>2</v>
@@ -1433,8 +1427,11 @@
       <c r="I2" s="9" t="s">
         <v>2</v>
       </c>
+      <c r="J2" s="9" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:9">
+    <row r="3" s="1" customFormat="1" spans="1:10">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -1462,60 +1459,69 @@
       <c r="I3" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="J3" s="5" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="4" ht="17" spans="1:9">
+    <row r="4" ht="17" customHeight="1" spans="1:10">
       <c r="A4" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="D4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="10">
         <v>41198</v>
-      </c>
-      <c r="G4" s="11">
-        <v>41384</v>
       </c>
       <c r="H4" s="11">
         <v>41384</v>
       </c>
-      <c r="I4" s="11"/>
+      <c r="I4" s="11">
+        <v>41384</v>
+      </c>
+      <c r="J4" s="11"/>
     </row>
-    <row r="5" ht="17" spans="1:9">
+    <row r="5" ht="17" customHeight="1" spans="1:10">
       <c r="A5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="10">
+      <c r="G5" s="10">
         <v>41183</v>
-      </c>
-      <c r="G5" s="11">
-        <v>41376</v>
       </c>
       <c r="H5" s="11">
         <v>41376</v>
       </c>
-      <c r="I5" s="11"/>
+      <c r="I5" s="11">
+        <v>41376</v>
+      </c>
+      <c r="J5" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">
